--- a/sports_forms/009_sports_psychology_referral_form--sports_forms.xlsx
+++ b/sports_forms/009_sports_psychology_referral_form--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>referral_form_athlete_details_label</t>
+          <t>referral_form_athlete_details_label_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>referral_form_athlete_details_label</t>
+          <t>referral_form_athlete_details_label_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>referral_form_athlete_details_label</t>
+          <t>referral_form_athlete_details_label_4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>referral_form_athlete_details_label</t>
+          <t>referral_form_athlete_details_label_5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>referral_form_athlete_details_label</t>
+          <t>referral_form_athlete_details_label_6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Contact Information</t>
+          <t>Referral Form Athlete Details Label 6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,7 +704,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>referral_form_athlete_details_label</t>
+          <t>referral_form_athlete_details_label_7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>referral_form_athlete_details_label</t>
+          <t>referral_form_athlete_details_label_8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>referral_form_next_steps</t>
+          <t>referral_form_next_steps_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>referral_form_next_steps</t>
+          <t>referral_form_next_steps_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>referral_form_next_steps</t>
+          <t>referral_form_next_steps_4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>referral_form_next_steps</t>
+          <t>referral_form_next_steps_5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Next Steps</t>
+          <t>Referral Form Next Steps 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>referral_form_next_steps</t>
+          <t>referral_form_next_steps_6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>referral_form_comments</t>
+          <t>referral_form_comments_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Referral Comments</t>
+          <t>Referral Form Comments 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,7 +934,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>referral_form_comments</t>
+          <t>referral_form_comments_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>referral_form_comments</t>
+          <t>referral_form_comments_4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>referral_form_comments</t>
+          <t>referral_form_comments_5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>referral_form_comments</t>
+          <t>referral_form_comments_6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Referral Comments</t>
+          <t>Referral Form Comments 6</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>referral_form_comments</t>
+          <t>referral_form_comments_7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>referral_form_comments</t>
+          <t>referral_form_comments_8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Follow-up Notes</t>
+          <t>Referral Form Comments 8</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="47" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +1126,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>referral_form_athlete_details_label_choices</t>
+          <t>referral_form_athlete_details_label_4_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>referral_form_athlete_details_label_choices</t>
+          <t>referral_form_athlete_details_label_4_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +1160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>referral_form_athlete_details_label_choices</t>
+          <t>referral_form_athlete_details_label_4_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
